--- a/nord-kivu/sortie/zs/Kalunguta/Tableaux_ZS_Kalunguta_20261014.xlsx
+++ b/nord-kivu/sortie/zs/Kalunguta/Tableaux_ZS_Kalunguta_20261014.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cas" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bulletin des aires'!$A$1:$P$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bulletin des aires'!$A$1:$P$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cas'!$A$1:$S$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,11 +452,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -558,25 +558,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Amini Yesu</t>
+          <t>Amani Kisungu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>52</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -585,28 +582,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Butuhe</t>
+          <t>Amini Yesu</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Verte</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -615,25 +609,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kabasha</t>
+          <t>Butuhe</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -645,27 +639,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kahamba</t>
+          <t>Cs Mwira</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
@@ -675,27 +663,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kalunguta</t>
+          <t>Hgr Kalunguta</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
@@ -705,27 +687,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kasebere</t>
+          <t>Isiale</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
@@ -735,7 +711,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kavakubi</t>
+          <t>Kabasha</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -744,16 +720,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -765,25 +741,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kivetya</t>
+          <t>Kahamba</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jaune</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -792,25 +771,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lisasa</t>
+          <t>Kajebere</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>21</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -819,25 +795,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mabo</t>
+          <t>Kalunguta</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Rouge</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
       <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
         <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>17</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -849,27 +825,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Maboya</t>
+          <t>Kanyihunga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
@@ -879,25 +849,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mambingi</t>
+          <t>Kasebene</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>50</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -906,7 +873,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mataba</t>
+          <t>Kasebere</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -915,16 +882,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -936,27 +903,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tinge</t>
+          <t>Kasitu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>14</v>
-      </c>
-      <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
@@ -966,32 +927,623 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Kavakubi</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kisungu</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kitovo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kivetya</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jaune</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>26</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kyangike</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kyasisogho</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kyavisogho</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lisasa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>21</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Mabingi</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mabo</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>17</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mabola</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Maboya</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>22</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mabuku</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mahohe</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Mambale</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mambingi</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Verte</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>50</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Mataba</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Mbilinga</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Rwahwa</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Tinge</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>14</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Virondo</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Visiki</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Vurondo</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Verte</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C38" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
         <v>69</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Vurundo</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P16"/>
+  <autoFilter ref="A1:P39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
